--- a/screen/screenList_protocolCore.xlsx
+++ b/screen/screenList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\screen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC57777E-93B8-4465-8AB7-1F48375FBCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DDB067-9A87-41E3-8208-6E573F0E67F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove videate" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="126">
   <si>
     <t>Cod Finestra</t>
   </si>
@@ -444,7 +444,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -569,91 +569,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -757,35 +677,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1066,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
@@ -1188,6 +1104,35 @@
       <c r="G5" s="35"/>
       <c r="H5" s="35"/>
       <c r="I5" s="35"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1211,7 +1156,7 @@
     <col min="10" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
@@ -1243,39 +1188,39 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="20">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1288,91 +1233,96 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="38" t="s">
+      <c r="B4" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="8">
         <v>5</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="38" t="s">
+      <c r="F4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="40" t="s">
+      <c r="H4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="44">
         <v>10</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="44">
         <v>500</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="15" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="9">
         <v>15</v>
       </c>
-      <c r="F6" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="44" t="s">
+      <c r="F6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="46" t="s">
+      <c r="H6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2468,7 +2418,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2507,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7DA8FE-E621-4698-863B-B0FF5EC6B02E}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2550,90 +2500,72 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="35" t="s">
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D3" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E3" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F3" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G3" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="H3" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D4" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E4" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F4" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="G5" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="35" t="s">
+      <c r="G4" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="43" t="s">
         <v>26</v>
       </c>
     </row>

--- a/screen/screenList_protocolCore.xlsx
+++ b/screen/screenList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\screen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DDB067-9A87-41E3-8208-6E573F0E67F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D16A4-B3B1-40E1-A57E-CEDEA99F4078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove videate" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="129">
   <si>
     <t>Cod Finestra</t>
   </si>
@@ -407,6 +407,15 @@
   </si>
   <si>
     <t>YAX3C</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>AMK</t>
+  </si>
+  <si>
+    <t>Note per  Patch</t>
   </si>
 </sst>
 </file>
@@ -444,7 +453,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -569,16 +578,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -677,9 +697,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -699,9 +716,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -982,157 +1008,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="J1" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="35" t="s">
+      <c r="J2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>77</v>
-      </c>
+      <c r="H3" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="43"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1157,172 +1193,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="18">
         <v>5</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="B4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <v>5</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="13" t="s">
+      <c r="H4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="2">
         <v>10</v>
       </c>
-      <c r="F5" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="2">
         <v>500</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>15</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="18" t="s">
+      <c r="H6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1356,155 +1392,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
     </row>
     <row r="3" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>1</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>1</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="H3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="6">
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="6">
         <v>1</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="26" t="s">
+      <c r="M3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" s="13" t="s">
+      <c r="R3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="29" t="s">
         <v>46</v>
       </c>
       <c r="E4">
@@ -1513,892 +1549,892 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="2">
         <v>1</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="27" t="s">
+      <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" s="15" t="s">
+      <c r="R4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="14">
         <v>1</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="14">
         <v>3</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="9">
+      <c r="H5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="7">
         <v>1</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="7">
         <v>1</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="28" t="s">
+      <c r="M5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="R5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="18" t="s">
+      <c r="R5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="33"/>
-      <c r="Q6" s="25"/>
+      <c r="D6" s="31"/>
+      <c r="Q6" s="23"/>
     </row>
     <row r="7" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>8</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="6">
         <v>1</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>4</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8">
+      <c r="K7" s="6"/>
+      <c r="L7" s="6">
         <v>15</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="26" t="s">
+      <c r="M7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="4"/>
+      <c r="R7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="T7" s="2"/>
     </row>
     <row r="8" spans="1:20" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>1</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="7">
         <v>44</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <v>15</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="28" t="s">
+      <c r="M8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="4"/>
+      <c r="S8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="2"/>
     </row>
     <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:20" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="18">
         <v>2</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="18">
         <v>7</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="18">
         <v>1</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="18">
         <v>4</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20" t="s">
+      <c r="K10" s="18"/>
+      <c r="L10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q10" s="29" t="s">
+      <c r="M10" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="R10" s="20" t="s">
+      <c r="R10" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="S10" s="21" t="s">
+      <c r="S10" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D11" s="25"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="H12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L12" s="35">
+      <c r="L12" s="33">
         <v>1</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="27" t="s">
+      <c r="M12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="R12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S12" s="4" t="s">
+      <c r="S12" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="H13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="33">
         <v>1</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q13" s="27" t="s">
+      <c r="M13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="R13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S13" s="4" t="s">
+      <c r="S13" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="4">
+      <c r="D14" s="29"/>
+      <c r="E14" s="2">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="4" t="s">
+      <c r="H14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="27" t="s">
+      <c r="K14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>2</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L15" s="35">
+      <c r="L15" s="33">
         <v>500</v>
       </c>
-      <c r="M15" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="O15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="P15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="27" t="s">
+      <c r="M15" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="S15" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>2</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>3</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="H16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="33">
         <v>500</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O16" s="4" t="s">
+      <c r="M16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="27" t="s">
+      <c r="P16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="R16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="S16" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="A17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>4</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="H17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="33">
         <v>500</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="27" t="s">
+      <c r="M17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="R17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="S17" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>5</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="H18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="2">
         <v>5</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="33">
         <v>500</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="27" t="s">
+      <c r="M18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="S18" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>2</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>6</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="H19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="35">
+      <c r="L19" s="33">
         <v>500</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="27" t="s">
+      <c r="M19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="S19" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="A20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>2</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>7</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <v>1</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="2">
         <v>4</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="33">
         <v>500</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="27" t="s">
+      <c r="M20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="R20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S20" s="4" t="s">
+      <c r="S20" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="A21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>3</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>1</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="H21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="33">
         <v>1</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="35" t="s">
+      <c r="M21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="R21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S21" s="4" t="s">
+      <c r="S21" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2418,35 +2454,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2472,100 +2508,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="39" t="s">
+      <c r="A3" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="40" t="s">
+      <c r="H3" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="37" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="A4" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="43" t="s">
+      <c r="G4" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="40" t="s">
         <v>26</v>
       </c>
     </row>
